--- a/reports/二级子公司D_现金流量表_2026-08.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-08.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>80982720</v>
+        <v>78840253</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>552996288</v>
+        <v>537236971</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1605376</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11561346</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>803443</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5785513</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>402623</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2891948</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>320429</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2312847</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>242154</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1736132</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>159955</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1155885</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>121155</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>868349</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>80008</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>577855</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>201649</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1447196</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>100748</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>726183</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>63933</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>459957</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>207648</v>
+        <v>201774</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1494324</v>
+        <v>1450522</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1384320</v>
+        <v>1340790</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>9962160</v>
+        <v>9670986</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>82574688</v>
+        <v>84484290</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>53065600</v>
+        <v>51739457</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>381882800</v>
+        <v>371096223</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>534093</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3852778</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>402583</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2893749</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>267843</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1927215</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>200651</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1446104</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>134333</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>964170</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>100575</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>726344</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8305920</v>
+        <v>8102311</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>59772960</v>
+        <v>58072792</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4383680</v>
+        <v>4234721</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>31546840</v>
+        <v>30601801</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1730400</v>
+        <v>1687940</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>12452700</v>
+        <v>12101105</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>67485600</v>
+        <v>67404507</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>15089088</v>
+        <v>17079783</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>80344</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>659200</v>
+        <v>640403</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>703477</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>5768000</v>
+        <v>5605182</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>418099</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3460800</v>
+        <v>3356867</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>783821</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>7981440</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>65920000</v>
+        <v>63957529</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1200942</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>9888000</v>
+        <v>9603991</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5504572</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>45320000</v>
+        <v>43994525</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>180895</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1483200</v>
+        <v>1441246</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8162335</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7378514</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1502756</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>12360000</v>
+        <v>12007069</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2496627</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>20600000</v>
+        <v>20000496</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2507038</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>20600000</v>
+        <v>20005538</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>79681</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>659200</v>
+        <v>639649</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4079064</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>1990000</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>16480000</v>
+        <v>15985597</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>2009472</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>16480000</v>
+        <v>16015060</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>318727</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2636800</v>
+        <v>2557735</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>279626</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2307200</v>
+        <v>2238862</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>39989</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>329600</v>
+        <v>320073</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2348716</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1730348</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>9238688</v>
+        <v>11431617</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>9238688</v>
+        <v>11431617</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
